--- a/input/点赞_用户列表.xlsx
+++ b/input/点赞_用户列表.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B159"/>
+  <dimension ref="A1:B513"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,7 +412,7 @@
         <v>岭右之家</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="3">
@@ -428,7 +428,7 @@
         <v>痛痛快快的去玩</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-02</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="5">
@@ -436,7 +436,7 @@
         <v>慕北家电精选</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="6">
@@ -444,7 +444,7 @@
         <v>豆豆的智慧百宝袋</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
     </row>
     <row r="7">
@@ -452,7 +452,7 @@
         <v>山上有艾的自留地</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="8">
@@ -460,7 +460,7 @@
         <v>精品日用百货</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="9">
@@ -468,7 +468,7 @@
         <v>全新闲置母婴好物</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>妮妮优选小家电</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="13">
@@ -508,7 +508,7 @@
         <v>品质家电严选社</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="15">
@@ -516,7 +516,7 @@
         <v>老罗搞数码</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>我是娜娜</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="18">
@@ -540,7 +540,7 @@
         <v>仙家好物</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="19">
@@ -548,7 +548,7 @@
         <v>幸运四叶草</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="20">
@@ -556,7 +556,7 @@
         <v>闽北土产薇薇</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="21">
@@ -572,7 +572,7 @@
         <v>麤麤酱二次元</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="23">
@@ -580,7 +580,7 @@
         <v>芋泥小卖家</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-01-02</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="24">
@@ -596,7 +596,7 @@
         <v>天冬家居馆</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="26">
@@ -620,7 +620,7 @@
         <v>蜗牛的赫利肯特价小铺</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="29">
@@ -636,7 +636,7 @@
         <v>星星落兜里</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="31">
@@ -644,7 +644,7 @@
         <v>靠谱好物优选</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="32">
@@ -668,7 +668,7 @@
         <v>小鱼精选</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="35">
@@ -676,7 +676,7 @@
         <v>精品家电小铺</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-01-04</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="36">
@@ -692,7 +692,7 @@
         <v>电子小当家</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="38">
@@ -700,7 +700,7 @@
         <v>敏敏生活百货</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="39">
@@ -708,7 +708,7 @@
         <v>品牌精选达人</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="40">
@@ -724,7 +724,7 @@
         <v>琳琳精品家电馆</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="42">
@@ -732,7 +732,7 @@
         <v>三七的风格小窝</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-14</v>
       </c>
     </row>
     <row r="43">
@@ -740,7 +740,7 @@
         <v>飒飒摩配</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-01-02</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="44">
@@ -748,7 +748,7 @@
         <v>枕星票务</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="45">
@@ -756,7 +756,7 @@
         <v>MiMi外设坊</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="46">
@@ -764,7 +764,7 @@
         <v>精品家电好物分享</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="47">
@@ -772,7 +772,7 @@
         <v>卖点干货</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="48">
@@ -788,7 +788,7 @@
         <v>美芽严选折扣店</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="50">
@@ -796,7 +796,7 @@
         <v>白猫不是喵</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="51">
@@ -804,7 +804,7 @@
         <v>潮玩小铺</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="52">
@@ -820,7 +820,7 @@
         <v>暖家优选家居</v>
       </c>
       <c r="B53" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="54">
@@ -828,7 +828,7 @@
         <v>雅雅精致宅</v>
       </c>
       <c r="B54" t="str">
-        <v>2026-01-04</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="55">
@@ -860,7 +860,7 @@
         <v>行星系馋嘴的多宝鱼</v>
       </c>
       <c r="B58" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="59">
@@ -868,7 +868,7 @@
         <v>小远在路上</v>
       </c>
       <c r="B59" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="60">
@@ -876,7 +876,7 @@
         <v>野思数码家电</v>
       </c>
       <c r="B60" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="61">
@@ -884,7 +884,7 @@
         <v>拿铁美式</v>
       </c>
       <c r="B61" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="62">
@@ -892,7 +892,7 @@
         <v>珊瑚海学摄影的帝王蟹</v>
       </c>
       <c r="B62" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="63">
@@ -908,7 +908,7 @@
         <v>瑶瑶的视听影院</v>
       </c>
       <c r="B64" t="str">
-        <v>2026-01-04</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="65">
@@ -940,7 +940,7 @@
         <v>壮壮公主的小铺</v>
       </c>
       <c r="B68" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="69">
@@ -948,7 +948,7 @@
         <v>苏苏活力补给小铺</v>
       </c>
       <c r="B69" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="70">
@@ -988,7 +988,7 @@
         <v>智能萌宠屋</v>
       </c>
       <c r="B74" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="75">
@@ -996,7 +996,7 @@
         <v>小公举的小铺铺</v>
       </c>
       <c r="B75" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="76">
@@ -1004,7 +1004,7 @@
         <v>忧郁烤面筋</v>
       </c>
       <c r="B76" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="77">
@@ -1028,7 +1028,7 @@
         <v>微光票务</v>
       </c>
       <c r="B79" t="str">
-        <v>2026-01-02</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="80">
@@ -1036,7 +1036,7 @@
         <v>桃子原单</v>
       </c>
       <c r="B80" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-14</v>
       </c>
     </row>
     <row r="81">
@@ -1052,7 +1052,7 @@
         <v>云云的精品家电</v>
       </c>
       <c r="B82" t="str">
-        <v>2026-01-04</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="83">
@@ -1060,7 +1060,7 @@
         <v>小刘电竞外设</v>
       </c>
       <c r="B83" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="84">
@@ -1068,7 +1068,7 @@
         <v>初安的秘密基地</v>
       </c>
       <c r="B84" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="85">
@@ -1092,7 +1092,7 @@
         <v>慵懒的橘子</v>
       </c>
       <c r="B87" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="88">
@@ -1100,7 +1100,7 @@
         <v>速度与科技</v>
       </c>
       <c r="B88" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="89">
@@ -1108,7 +1108,7 @@
         <v>戴森到家</v>
       </c>
       <c r="B89" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="90">
@@ -1132,7 +1132,7 @@
         <v>电竞游戏外设店铺</v>
       </c>
       <c r="B92" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="93">
@@ -1148,7 +1148,7 @@
         <v>解忧杂货铺</v>
       </c>
       <c r="B94" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="95">
@@ -1156,7 +1156,7 @@
         <v>有趣的鱼次元屋</v>
       </c>
       <c r="B95" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="96">
@@ -1164,7 +1164,7 @@
         <v>妤梓欣欣</v>
       </c>
       <c r="B96" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="97">
@@ -1188,7 +1188,7 @@
         <v>甜豆数码耳机</v>
       </c>
       <c r="B99" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="100">
@@ -1196,7 +1196,7 @@
         <v>小鱼家电优选</v>
       </c>
       <c r="B100" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="101">
@@ -1212,7 +1212,7 @@
         <v>小me优选</v>
       </c>
       <c r="B102" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="103">
@@ -1220,7 +1220,7 @@
         <v>精品数码馆</v>
       </c>
       <c r="B103" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="104">
@@ -1236,7 +1236,7 @@
         <v>中政张律</v>
       </c>
       <c r="B105" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="106">
@@ -1252,7 +1252,7 @@
         <v>黑猫卡券</v>
       </c>
       <c r="B107" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="108">
@@ -1260,7 +1260,7 @@
         <v>沐沐谷屋</v>
       </c>
       <c r="B108" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="109">
@@ -1276,7 +1276,7 @@
         <v>绣江小家电中心</v>
       </c>
       <c r="B110" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-14</v>
       </c>
     </row>
     <row r="111">
@@ -1284,7 +1284,7 @@
         <v>蹦哒辣椒</v>
       </c>
       <c r="B111" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="112">
@@ -1292,7 +1292,7 @@
         <v>暖妈家外贸床品</v>
       </c>
       <c r="B112" t="str">
-        <v>2026-01-04</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="113">
@@ -1316,7 +1316,7 @@
         <v>开心生活馆</v>
       </c>
       <c r="B115" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="116">
@@ -1332,7 +1332,7 @@
         <v>可可精品家居馆</v>
       </c>
       <c r="B117" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-14</v>
       </c>
     </row>
     <row r="118">
@@ -1340,7 +1340,7 @@
         <v>阿陈陈陈</v>
       </c>
       <c r="B118" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="119">
@@ -1356,7 +1356,7 @@
         <v>梓莹精品</v>
       </c>
       <c r="B120" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="121">
@@ -1364,7 +1364,7 @@
         <v>白绝火影代肝</v>
       </c>
       <c r="B121" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="122">
@@ -1372,7 +1372,7 @@
         <v>吕小花儿开</v>
       </c>
       <c r="B122" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="123">
@@ -1404,7 +1404,7 @@
         <v>暖居家电铺</v>
       </c>
       <c r="B126" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="127">
@@ -1412,7 +1412,7 @@
         <v>陆陆潮玩</v>
       </c>
       <c r="B127" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="128">
@@ -1420,7 +1420,7 @@
         <v>家居好物</v>
       </c>
       <c r="B128" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-14</v>
       </c>
     </row>
     <row r="129">
@@ -1428,7 +1428,7 @@
         <v>宅家鼠鼠</v>
       </c>
       <c r="B129" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="130">
@@ -1444,7 +1444,7 @@
         <v>TT游戏店</v>
       </c>
       <c r="B131" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="132">
@@ -1476,7 +1476,7 @@
         <v>七宝的小铺子</v>
       </c>
       <c r="B135" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="136">
@@ -1484,7 +1484,7 @@
         <v>在逃二次元周边</v>
       </c>
       <c r="B136" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="137">
@@ -1500,7 +1500,7 @@
         <v>南朝攒钱的甜圈</v>
       </c>
       <c r="B138" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="139">
@@ -1524,7 +1524,7 @@
         <v>二次元在逃大佛</v>
       </c>
       <c r="B141" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="142">
@@ -1532,7 +1532,7 @@
         <v>小源精品数码</v>
       </c>
       <c r="B142" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-06</v>
       </c>
     </row>
     <row r="143">
@@ -1540,7 +1540,7 @@
         <v>晓晓数码</v>
       </c>
       <c r="B143" t="str">
-        <v>2026-01-04</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="144">
@@ -1548,7 +1548,7 @@
         <v>睡个甜甜的宝可梦</v>
       </c>
       <c r="B144" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="145">
@@ -1556,7 +1556,7 @@
         <v>蓝胖子的小店</v>
       </c>
       <c r="B145" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="146">
@@ -1564,7 +1564,7 @@
         <v>玉子市场</v>
       </c>
       <c r="B146" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="147">
@@ -1588,7 +1588,7 @@
         <v>啊啊啊啊嘘</v>
       </c>
       <c r="B149" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-18</v>
       </c>
     </row>
     <row r="150">
@@ -1596,7 +1596,7 @@
         <v>蟹蟹的模玩世界</v>
       </c>
       <c r="B150" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-20</v>
       </c>
     </row>
     <row r="151">
@@ -1636,7 +1636,7 @@
         <v>CC妙脆角</v>
       </c>
       <c r="B155" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-14</v>
       </c>
     </row>
     <row r="156">
@@ -1644,7 +1644,7 @@
         <v>日光城的童书绘本馆</v>
       </c>
       <c r="B156" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-15</v>
       </c>
     </row>
     <row r="157">
@@ -1652,7 +1652,7 @@
         <v>精品家电合作社</v>
       </c>
       <c r="B157" t="str">
-        <v>2026-01-04</v>
+        <v>2026-01-17</v>
       </c>
     </row>
     <row r="158">
@@ -1660,7 +1660,7 @@
         <v>妙妙的后备仓</v>
       </c>
       <c r="B158" t="str">
-        <v>2026-01-04</v>
+        <v>2026-02-06</v>
       </c>
     </row>
     <row r="159">
@@ -1671,9 +1671,2841 @@
         <v>2026-01-04</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>芋头的智能家电小站</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>CL数码小栈</v>
+      </c>
+      <c r="B161" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>暖暖的美妆象限</v>
+      </c>
+      <c r="B162" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>黄铜刮痧理疗自学中医</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>愤怒小呆呆</v>
+      </c>
+      <c r="B164" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>小怡潮玩</v>
+      </c>
+      <c r="B165" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>吊桥很哇塞的小青龙</v>
+      </c>
+      <c r="B166" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>咣当一颗心</v>
+      </c>
+      <c r="B167" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>电鸡小公主会翘头</v>
+      </c>
+      <c r="B168" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>多米正品美妆铺</v>
+      </c>
+      <c r="B169" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>奕新甄选</v>
+      </c>
+      <c r="B170" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>行吗实惠正品</v>
+      </c>
+      <c r="B171" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>小鱼数码</v>
+      </c>
+      <c r="B172" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>用我的杯杯喝口水</v>
+      </c>
+      <c r="B173" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v/>
+      </c>
+      <c r="B174" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>小牛外贸水杯屋</v>
+      </c>
+      <c r="B175" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>里物潮玩</v>
+      </c>
+      <c r="B176" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>质造生活社</v>
+      </c>
+      <c r="B177" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>胧月优品</v>
+      </c>
+      <c r="B178" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>逐梦电竞小布丁</v>
+      </c>
+      <c r="B179" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>萱萱生活好物</v>
+      </c>
+      <c r="B180" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>玥玥严选小铺</v>
+      </c>
+      <c r="B181" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>专业的人卖专业的产品</v>
+      </c>
+      <c r="B182" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>数码闪存小铺</v>
+      </c>
+      <c r="B183" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>梆梆就暴富小家电</v>
+      </c>
+      <c r="B184" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>月月正品折扣店</v>
+      </c>
+      <c r="B185" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>豆子小优选</v>
+      </c>
+      <c r="B186" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>泡泡的盲盒屋</v>
+      </c>
+      <c r="B187" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>行走的3D</v>
+      </c>
+      <c r="B188" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>谦谦君子卑以自牧</v>
+      </c>
+      <c r="B189" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>飞科正品代理</v>
+      </c>
+      <c r="B190" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>家电大王</v>
+      </c>
+      <c r="B191" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>云影逸梦</v>
+      </c>
+      <c r="B192" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>蔷薇花的杂货铺</v>
+      </c>
+      <c r="B193" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>咖啡馆熟练的毛肚</v>
+      </c>
+      <c r="B194" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>梦在云端3211</v>
+      </c>
+      <c r="B195" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>言寺家电精选屋</v>
+      </c>
+      <c r="B196" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>青柚数码科技</v>
+      </c>
+      <c r="B197" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>乐乐数码工坊</v>
+      </c>
+      <c r="B198" t="str">
+        <v>2026-01-06</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>精选电器生活馆</v>
+      </c>
+      <c r="B199" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>数码家电优选仓</v>
+      </c>
+      <c r="B200" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>种子星球绘本馆</v>
+      </c>
+      <c r="B201" t="str">
+        <v>2026-01-13</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>像风像云像雾</v>
+      </c>
+      <c r="B202" t="str">
+        <v>2026-01-13</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>小树啦啦啦</v>
+      </c>
+      <c r="B203" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>居家好物</v>
+      </c>
+      <c r="B204" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>包袋简选</v>
+      </c>
+      <c r="B205" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>优质小家电</v>
+      </c>
+      <c r="B206" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>汤米捏捏手作</v>
+      </c>
+      <c r="B207" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>小米空气净化器</v>
+      </c>
+      <c r="B208" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>莫言會拍照</v>
+      </c>
+      <c r="B209" t="str">
+        <v>2026-01-13</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>之魄2026</v>
+      </c>
+      <c r="B210" t="str">
+        <v>2026-01-13</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>心爱的小车车</v>
+      </c>
+      <c r="B211" t="str">
+        <v>2026-01-13</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>丶云霄丶</v>
+      </c>
+      <c r="B212" t="str">
+        <v>2026-01-13</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>柚橙家居坊</v>
+      </c>
+      <c r="B213" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>芝士小熊</v>
+      </c>
+      <c r="B214" t="str">
+        <v>2026-01-13</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>小艾解忧铺</v>
+      </c>
+      <c r="B215" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>优选好物</v>
+      </c>
+      <c r="B216" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>妖精潮玩</v>
+      </c>
+      <c r="B217" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>大洋洲真诚的冠毛鱼</v>
+      </c>
+      <c r="B218" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>咋啦小店</v>
+      </c>
+      <c r="B219" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>北纬扒蒜的海狼</v>
+      </c>
+      <c r="B220" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>一淼潮玩</v>
+      </c>
+      <c r="B221" t="str">
+        <v>2026-01-13</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>关关诚信数码</v>
+      </c>
+      <c r="B222" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>八十一条咸鱼</v>
+      </c>
+      <c r="B223" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>蓝鲸甄选</v>
+      </c>
+      <c r="B224" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>TLT潮玩</v>
+      </c>
+      <c r="B225" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>仓库直发</v>
+      </c>
+      <c r="B226" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>喵星人小二的铺子</v>
+      </c>
+      <c r="B227" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>精选工厂店</v>
+      </c>
+      <c r="B228" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>黄黄的玩具手办</v>
+      </c>
+      <c r="B229" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>鱼鱼百货</v>
+      </c>
+      <c r="B230" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>何方工厂女孩</v>
+      </c>
+      <c r="B231" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>暖居时光集</v>
+      </c>
+      <c r="B232" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>派秋SAMA</v>
+      </c>
+      <c r="B233" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>玲玲家电</v>
+      </c>
+      <c r="B234" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>北冰洋不冰</v>
+      </c>
+      <c r="B235" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>马克tu油</v>
+      </c>
+      <c r="B236" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>家居电器</v>
+      </c>
+      <c r="B237" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>懒人拯救计划</v>
+      </c>
+      <c r="B238" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>小新杂货铺</v>
+      </c>
+      <c r="B239" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>lucky</v>
+      </c>
+      <c r="B240" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>早早宠物用品仓库</v>
+      </c>
+      <c r="B241" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>财源滚滚</v>
+      </c>
+      <c r="B242" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>非常幸运的无人机</v>
+      </c>
+      <c r="B243" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>无人机代理</v>
+      </c>
+      <c r="B244" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>巴斯家的暖心小家电</v>
+      </c>
+      <c r="B245" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>拾光图书</v>
+      </c>
+      <c r="B246" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>永远是个杯控</v>
+      </c>
+      <c r="B247" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>东东潮流盲盒</v>
+      </c>
+      <c r="B248" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>雪梨桃胶</v>
+      </c>
+      <c r="B249" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>海绵奇幻堡</v>
+      </c>
+      <c r="B250" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>没有雷区的阿沐</v>
+      </c>
+      <c r="B251" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>居家小电严选</v>
+      </c>
+      <c r="B252" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>繁花血景</v>
+      </c>
+      <c r="B253" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>航拍极客</v>
+      </c>
+      <c r="B254" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>商朝处女座平菇</v>
+      </c>
+      <c r="B255" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>萌萌小熊猫</v>
+      </c>
+      <c r="B256" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>轻航数码铺</v>
+      </c>
+      <c r="B257" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>优品橱窗</v>
+      </c>
+      <c r="B258" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>鲸九配件</v>
+      </c>
+      <c r="B259" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>文文资源馆</v>
+      </c>
+      <c r="B260" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>小小小鱼儿</v>
+      </c>
+      <c r="B261" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>元气毛绒补给站</v>
+      </c>
+      <c r="B262" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>洋葱日用小家电</v>
+      </c>
+      <c r="B263" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>和气大掌柜</v>
+      </c>
+      <c r="B264" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>精品吹风供应小杨</v>
+      </c>
+      <c r="B265" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>墨丘利的糖果</v>
+      </c>
+      <c r="B266" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>佩尼Panny</v>
+      </c>
+      <c r="B267" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>鱼蛙健身装备仓</v>
+      </c>
+      <c r="B268" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>一颗奶糖呀</v>
+      </c>
+      <c r="B269" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>吹呀吹丰</v>
+      </c>
+      <c r="B270" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>噗噗优选好物</v>
+      </c>
+      <c r="B271" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>不止于此</v>
+      </c>
+      <c r="B272" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>马美丽的时尚购物清单</v>
+      </c>
+      <c r="B273" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>是阿喵呀</v>
+      </c>
+      <c r="B274" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>糖豆桌游优选馆</v>
+      </c>
+      <c r="B275" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>玩物饰集</v>
+      </c>
+      <c r="B276" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>爱家生活家居</v>
+      </c>
+      <c r="B277" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>孤城洛雪的数码小店</v>
+      </c>
+      <c r="B278" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>荒岛甜甜的红参</v>
+      </c>
+      <c r="B279" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>穎家优品甄選</v>
+      </c>
+      <c r="B280" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>康康智能小电器</v>
+      </c>
+      <c r="B281" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>数码专业玩家</v>
+      </c>
+      <c r="B282" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>小田杂货铺</v>
+      </c>
+      <c r="B283" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>暖暖工厂店</v>
+      </c>
+      <c r="B284" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>尊妮优品</v>
+      </c>
+      <c r="B285" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>晓可儿鸭</v>
+      </c>
+      <c r="B286" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>奶油潮玩铺</v>
+      </c>
+      <c r="B287" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v/>
+      </c>
+      <c r="B288" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>老胡卖家电</v>
+      </c>
+      <c r="B289" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>何果子老师的授课</v>
+      </c>
+      <c r="B290" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>迪士尼儿崽崽收藏家</v>
+      </c>
+      <c r="B291" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>妙妙姐天天摸大红</v>
+      </c>
+      <c r="B292" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>钛美咯大劳</v>
+      </c>
+      <c r="B293" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>朵朵捡漏清仓</v>
+      </c>
+      <c r="B294" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>一家老店</v>
+      </c>
+      <c r="B295" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>何果子爱吃饭</v>
+      </c>
+      <c r="B296" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>也是小丸子呀</v>
+      </c>
+      <c r="B297" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>欣欣精品小家电</v>
+      </c>
+      <c r="B298" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>采花椒的小姑凉</v>
+      </c>
+      <c r="B299" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>省心优选家电馆</v>
+      </c>
+      <c r="B300" t="str">
+        <v>2026-01-14</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>精品积木小屋</v>
+      </c>
+      <c r="B301" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>清婉若兮</v>
+      </c>
+      <c r="B302" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>挪威唱民歌的芝士</v>
+      </c>
+      <c r="B303" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>酷酷的数码店</v>
+      </c>
+      <c r="B304" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>七七严选</v>
+      </c>
+      <c r="B305" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>楼兰宝藏屋</v>
+      </c>
+      <c r="B306" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>方方LT</v>
+      </c>
+      <c r="B307" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>豪爽的秋葵</v>
+      </c>
+      <c r="B308" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>幸福康养</v>
+      </c>
+      <c r="B309" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>宅家睡懒觉</v>
+      </c>
+      <c r="B310" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>干货资料中转站</v>
+      </c>
+      <c r="B311" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>阿瑶的共享站</v>
+      </c>
+      <c r="B312" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>相宜又纵然</v>
+      </c>
+      <c r="B313" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>不吃香菜资源库</v>
+      </c>
+      <c r="B314" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>饱饱米家好物</v>
+      </c>
+      <c r="B315" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>马年周边</v>
+      </c>
+      <c r="B316" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>淘闲小栈</v>
+      </c>
+      <c r="B317" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>天天正品折扣店</v>
+      </c>
+      <c r="B318" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>月月资料库</v>
+      </c>
+      <c r="B319" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v/>
+      </c>
+      <c r="B320" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>染染的宝屋</v>
+      </c>
+      <c r="B321" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>奇想造物集</v>
+      </c>
+      <c r="B322" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>小鱼电器铺</v>
+      </c>
+      <c r="B323" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>爱喝白开水</v>
+      </c>
+      <c r="B324" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>明天不吃面包</v>
+      </c>
+      <c r="B325" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>挽挽数码</v>
+      </c>
+      <c r="B326" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>autism票务</v>
+      </c>
+      <c r="B327" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>娜娜是我呀</v>
+      </c>
+      <c r="B328" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>无刺迷羽</v>
+      </c>
+      <c r="B329" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>银河健身队</v>
+      </c>
+      <c r="B330" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>华东清爽的芒果</v>
+      </c>
+      <c r="B331" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>卡萨布兰卡</v>
+      </c>
+      <c r="B332" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>巴啦啦能量</v>
+      </c>
+      <c r="B333" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>小琳甄选铺</v>
+      </c>
+      <c r="B334" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>帮帮家具工厂店</v>
+      </c>
+      <c r="B335" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>安安妈妈</v>
+      </c>
+      <c r="B336" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>招财猫的小叮当</v>
+      </c>
+      <c r="B337" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>西西的家</v>
+      </c>
+      <c r="B338" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>流云小家电</v>
+      </c>
+      <c r="B339" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>武鸣精诚电器</v>
+      </c>
+      <c r="B340" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>虎妈俩萌娃</v>
+      </c>
+      <c r="B341" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>米饭rice</v>
+      </c>
+      <c r="B342" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>阿倩爱喝水</v>
+      </c>
+      <c r="B343" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>coco放假了哦</v>
+      </c>
+      <c r="B344" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>九号魔女配件</v>
+      </c>
+      <c r="B345" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>六六数码宝贝</v>
+      </c>
+      <c r="B346" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>粥粥爱喝粥</v>
+      </c>
+      <c r="B347" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>快乐吖吖</v>
+      </c>
+      <c r="B348" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>samsam爱旅行</v>
+      </c>
+      <c r="B349" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>ELVALINTARA</v>
+      </c>
+      <c r="B350" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>逐梦的小萌</v>
+      </c>
+      <c r="B351" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>小桔子家电批发</v>
+      </c>
+      <c r="B352" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>木米小铺</v>
+      </c>
+      <c r="B353" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>青悦小米扫地机优选店</v>
+      </c>
+      <c r="B354" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Zephyr音响</v>
+      </c>
+      <c r="B355" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>小黑的花语驿站</v>
+      </c>
+      <c r="B356" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>卖追觅的小姐姐</v>
+      </c>
+      <c r="B357" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>大牌护肤代购</v>
+      </c>
+      <c r="B358" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>精品家居生活馆</v>
+      </c>
+      <c r="B359" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>萌米小圈宠物用品店</v>
+      </c>
+      <c r="B360" t="str">
+        <v>2026-01-15</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v/>
+      </c>
+      <c r="B361" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>元气水杯馆</v>
+      </c>
+      <c r="B362" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>零点剧场</v>
+      </c>
+      <c r="B363" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>橘色日落香氛</v>
+      </c>
+      <c r="B364" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>米米酱好物</v>
+      </c>
+      <c r="B365" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>3D打印工作室</v>
+      </c>
+      <c r="B366" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>神奇小屋阁</v>
+      </c>
+      <c r="B367" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>键盘鼠标精品小铺</v>
+      </c>
+      <c r="B368" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>彩虹光学</v>
+      </c>
+      <c r="B369" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>明发精品数码家电</v>
+      </c>
+      <c r="B370" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>大小咩咩</v>
+      </c>
+      <c r="B371" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>無印良倉</v>
+      </c>
+      <c r="B372" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>母婴好物店</v>
+      </c>
+      <c r="B373" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>琳琳姐姐</v>
+      </c>
+      <c r="B374" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>小绿免税店清仓</v>
+      </c>
+      <c r="B375" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>阿巴巴巴</v>
+      </c>
+      <c r="B376" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>婉婉精选家电馆</v>
+      </c>
+      <c r="B377" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>糯米粒的有趣小屋</v>
+      </c>
+      <c r="B378" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>喜帖街心惊胆战的翻车鱼</v>
+      </c>
+      <c r="B379" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>淡淡的咸鱼</v>
+      </c>
+      <c r="B380" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>次元回血站</v>
+      </c>
+      <c r="B381" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>一钛清饮</v>
+      </c>
+      <c r="B382" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>爪爪好物集</v>
+      </c>
+      <c r="B383" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>饼干麻麻挑好物的店</v>
+      </c>
+      <c r="B384" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>呢喃的玩具铺</v>
+      </c>
+      <c r="B385" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>章丘宗匠铁锅传承</v>
+      </c>
+      <c r="B386" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>阿狸在小鱼</v>
+      </c>
+      <c r="B387" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>手办定制Z初代奶芯</v>
+      </c>
+      <c r="B388" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>麦芽的悦物集</v>
+      </c>
+      <c r="B389" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>设计院提桶的女工</v>
+      </c>
+      <c r="B390" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>悦活元素</v>
+      </c>
+      <c r="B391" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>水果粒儿</v>
+      </c>
+      <c r="B392" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>初见你时饰品集</v>
+      </c>
+      <c r="B393" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>菠萝小店</v>
+      </c>
+      <c r="B394" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>二次元玩家</v>
+      </c>
+      <c r="B395" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>北冰洋高情商的珍珠贝</v>
+      </c>
+      <c r="B396" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>叶子家居</v>
+      </c>
+      <c r="B397" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>超哥的破船</v>
+      </c>
+      <c r="B398" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>薇薇万事屋</v>
+      </c>
+      <c r="B399" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>萌萌小樱桃</v>
+      </c>
+      <c r="B400" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>神奇红蘑菇的资源库</v>
+      </c>
+      <c r="B401" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>家电小栈</v>
+      </c>
+      <c r="B402" t="str">
+        <v>2026-01-17</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>小松松子</v>
+      </c>
+      <c r="B403" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>真诚的冠毛鱼</v>
+      </c>
+      <c r="B404" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>吃小鱼干的柠檬小咪</v>
+      </c>
+      <c r="B405" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>TLOLT</v>
+      </c>
+      <c r="B406" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>小羊家电馆</v>
+      </c>
+      <c r="B407" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>正义法师</v>
+      </c>
+      <c r="B408" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>精品萌娃周边</v>
+      </c>
+      <c r="B409" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>在线的人都</v>
+      </c>
+      <c r="B410" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>流云数码好物</v>
+      </c>
+      <c r="B411" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>zz心</v>
+      </c>
+      <c r="B412" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>超哥杂货铺</v>
+      </c>
+      <c r="B413" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>小楠学姐</v>
+      </c>
+      <c r="B414" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>萌趣盲盒屋</v>
+      </c>
+      <c r="B415" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>小鱼的思维泡泡</v>
+      </c>
+      <c r="B416" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>TLT托</v>
+      </c>
+      <c r="B417" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>想上岸的海豚</v>
+      </c>
+      <c r="B418" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>powehi_-_</v>
+      </c>
+      <c r="B419" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>零隙三角洲</v>
+      </c>
+      <c r="B420" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>牧云读博中</v>
+      </c>
+      <c r="B421" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>是牧云呀</v>
+      </c>
+      <c r="B422" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>洛洛爱吃鱼</v>
+      </c>
+      <c r="B423" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>幸运盲盒社</v>
+      </c>
+      <c r="B424" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>天上掉下萝卜花</v>
+      </c>
+      <c r="B425" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>松松小屋</v>
+      </c>
+      <c r="B426" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>娜娜的口袋</v>
+      </c>
+      <c r="B427" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>周边补给站</v>
+      </c>
+      <c r="B428" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>芝士奶球</v>
+      </c>
+      <c r="B429" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>穎致严选</v>
+      </c>
+      <c r="B430" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>山东老李丨铁匠世家</v>
+      </c>
+      <c r="B431" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>虫乃的打印小铺</v>
+      </c>
+      <c r="B432" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>半岛元气满满的深海章鱼</v>
+      </c>
+      <c r="B433" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>布布潮玩</v>
+      </c>
+      <c r="B434" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>轻奢珠宝种草屋</v>
+      </c>
+      <c r="B435" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>拾光杂货铺</v>
+      </c>
+      <c r="B436" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>工厂清仓小助手</v>
+      </c>
+      <c r="B437" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v/>
+      </c>
+      <c r="B438" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>熊猫Elvira</v>
+      </c>
+      <c r="B439" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>小启的宝藏</v>
+      </c>
+      <c r="B440" t="str">
+        <v>2026-01-18</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>小琳子家充电宝</v>
+      </c>
+      <c r="B441" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>小店萌主</v>
+      </c>
+      <c r="B442" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>清河南鸢</v>
+      </c>
+      <c r="B443" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>爱生活的阿超</v>
+      </c>
+      <c r="B444" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>杯趣生活</v>
+      </c>
+      <c r="B445" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>全新精品小家电馆</v>
+      </c>
+      <c r="B446" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>Lucky的杂货铺</v>
+      </c>
+      <c r="B447" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>牛牛说是</v>
+      </c>
+      <c r="B448" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>哇塞设计小铺</v>
+      </c>
+      <c r="B449" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>626魔法屋</v>
+      </c>
+      <c r="B450" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>左海明亮的饼干</v>
+      </c>
+      <c r="B451" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>正法老李</v>
+      </c>
+      <c r="B452" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>潮电集合站</v>
+      </c>
+      <c r="B453" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>花开半夏</v>
+      </c>
+      <c r="B454" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>爱吃鱼的黄八八</v>
+      </c>
+      <c r="B455" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>小源的游戏小屋</v>
+      </c>
+      <c r="B456" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>数码小雷达</v>
+      </c>
+      <c r="B457" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>做小家电日用的小双</v>
+      </c>
+      <c r="B458" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>小河数码丨回收二手电脑</v>
+      </c>
+      <c r="B459" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>午夜私趣馆</v>
+      </c>
+      <c r="B460" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>航海家S尾单</v>
+      </c>
+      <c r="B461" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>精品家居小店</v>
+      </c>
+      <c r="B462" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>balabala&amp;pi;</v>
+      </c>
+      <c r="B463" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v/>
+      </c>
+      <c r="B464" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>进口乳胶线下折扣</v>
+      </c>
+      <c r="B465" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>美佳小家电</v>
+      </c>
+      <c r="B466" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>宝藏耳机挖挖看</v>
+      </c>
+      <c r="B467" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>月月正品小家电</v>
+      </c>
+      <c r="B468" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>潮玩小窝</v>
+      </c>
+      <c r="B469" t="str">
+        <v>2026-01-20</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v/>
+      </c>
+      <c r="B470" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>渠道内购</v>
+      </c>
+      <c r="B471" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>杯杯精品馆</v>
+      </c>
+      <c r="B472" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>Zz家用电器生活馆</v>
+      </c>
+      <c r="B473" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>欣心潮玩铺</v>
+      </c>
+      <c r="B474" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>小桃的放映盒</v>
+      </c>
+      <c r="B475" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>绘夜Huirato</v>
+      </c>
+      <c r="B476" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>未央好物铺</v>
+      </c>
+      <c r="B477" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>糯糯不迷路</v>
+      </c>
+      <c r="B478" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>青柠数码小铺</v>
+      </c>
+      <c r="B479" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>暖家优选小家电</v>
+      </c>
+      <c r="B480" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>早上死不起</v>
+      </c>
+      <c r="B481" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>淘低价券</v>
+      </c>
+      <c r="B482" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>品质数码小家电鱼铺</v>
+      </c>
+      <c r="B483" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>好好树码</v>
+      </c>
+      <c r="B484" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>设计师小飞</v>
+      </c>
+      <c r="B485" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>玩偶柜子</v>
+      </c>
+      <c r="B486" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>卷卷毛毛</v>
+      </c>
+      <c r="B487" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>奶味饼干</v>
+      </c>
+      <c r="B488" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>拾叁同学数码</v>
+      </c>
+      <c r="B489" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>精品宝藏馆</v>
+      </c>
+      <c r="B490" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>强者资源库</v>
+      </c>
+      <c r="B491" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>小小的晓</v>
+      </c>
+      <c r="B492" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>品牌高端厨卫精品店</v>
+      </c>
+      <c r="B493" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>杯中有光</v>
+      </c>
+      <c r="B494" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>果汁的闲置杂货铺</v>
+      </c>
+      <c r="B495" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>李小鸣鱼鱼</v>
+      </c>
+      <c r="B496" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>曼波小家电</v>
+      </c>
+      <c r="B497" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
+        <v>情趣橘子</v>
+      </c>
+      <c r="B498" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>电子数码大掌柜</v>
+      </c>
+      <c r="B499" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>全能运动好物铺</v>
+      </c>
+      <c r="B500" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>幽兰精品数码</v>
+      </c>
+      <c r="B501" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
+        <v>清洁家电精品馆</v>
+      </c>
+      <c r="B502" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>薇薇京东正品仓</v>
+      </c>
+      <c r="B503" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>爆款家电严选小铺</v>
+      </c>
+      <c r="B504" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>奔速美学</v>
+      </c>
+      <c r="B505" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>奥莱折扣商品</v>
+      </c>
+      <c r="B506" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>云边煮清粥</v>
+      </c>
+      <c r="B507" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>来自科技星球</v>
+      </c>
+      <c r="B508" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>红红火火</v>
+      </c>
+      <c r="B509" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>MOVA智能家电城</v>
+      </c>
+      <c r="B510" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>水鱼糯糯</v>
+      </c>
+      <c r="B511" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
+        <v>虾条星人</v>
+      </c>
+      <c r="B512" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>小敏家电严选</v>
+      </c>
+      <c r="B513" t="str">
+        <v>2026-02-06</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B159"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B513"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/input/点赞_用户列表.xlsx
+++ b/input/点赞_用户列表.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B556"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -572,7 +572,7 @@
         <v>麤麤酱二次元</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-01-20</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="23">
@@ -1524,7 +1524,7 @@
         <v>二次元在逃大佛</v>
       </c>
       <c r="B141" t="str">
-        <v>2026-01-17</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="142">
@@ -1636,7 +1636,7 @@
         <v>CC妙脆角</v>
       </c>
       <c r="B155" t="str">
-        <v>2026-01-14</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="156">
@@ -2068,7 +2068,7 @@
         <v>莫言會拍照</v>
       </c>
       <c r="B209" t="str">
-        <v>2026-01-13</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="210">
@@ -2116,7 +2116,7 @@
         <v>小艾解忧铺</v>
       </c>
       <c r="B215" t="str">
-        <v>2026-01-18</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="216">
@@ -2820,7 +2820,7 @@
         <v>挪威唱民歌的芝士</v>
       </c>
       <c r="B303" t="str">
-        <v>2026-02-06</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="304">
@@ -3212,7 +3212,7 @@
         <v>小桔子家电批发</v>
       </c>
       <c r="B352" t="str">
-        <v>2026-01-20</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="353">
@@ -3436,7 +3436,7 @@
         <v>淡淡的咸鱼</v>
       </c>
       <c r="B380" t="str">
-        <v>2026-01-17</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="381">
@@ -3812,7 +3812,7 @@
         <v>娜娜的口袋</v>
       </c>
       <c r="B427" t="str">
-        <v>2026-01-18</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="428">
@@ -4236,7 +4236,7 @@
         <v>暖家优选小家电</v>
       </c>
       <c r="B480" t="str">
-        <v>2026-02-06</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="481">
@@ -4324,7 +4324,7 @@
         <v>强者资源库</v>
       </c>
       <c r="B491" t="str">
-        <v>2026-02-06</v>
+        <v>2026-03-22</v>
       </c>
     </row>
     <row r="492">
@@ -4503,9 +4503,353 @@
         <v>2026-02-06</v>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>柠源优品</v>
+      </c>
+      <c r="B514" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>甜净生活馆</v>
+      </c>
+      <c r="B515" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>壹人小家电</v>
+      </c>
+      <c r="B516" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v/>
+      </c>
+      <c r="B517" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>橘子味的秋天</v>
+      </c>
+      <c r="B518" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>品质家电严选店</v>
+      </c>
+      <c r="B519" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>小杨数码科技</v>
+      </c>
+      <c r="B520" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>智享科技</v>
+      </c>
+      <c r="B521" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>伊伊家电</v>
+      </c>
+      <c r="B522" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>羽球小哥的二手球</v>
+      </c>
+      <c r="B523" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>小云严选数码</v>
+      </c>
+      <c r="B524" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>狸狸次元屋</v>
+      </c>
+      <c r="B525" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>毛毛的玩偶屋</v>
+      </c>
+      <c r="B526" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>G小王子</v>
+      </c>
+      <c r="B527" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>小枝百货铺</v>
+      </c>
+      <c r="B528" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
+        <v>大鱼和小余店铺</v>
+      </c>
+      <c r="B529" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
+        <v>布偶猫的百宝袋</v>
+      </c>
+      <c r="B530" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>乐乐严选家电</v>
+      </c>
+      <c r="B531" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>小E的宝藏清单</v>
+      </c>
+      <c r="B532" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>美术馆会玩的翻车鱼</v>
+      </c>
+      <c r="B533" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>诚品数码铺</v>
+      </c>
+      <c r="B534" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>海伦的小店铺</v>
+      </c>
+      <c r="B535" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>快乐小宝</v>
+      </c>
+      <c r="B536" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>六一小仙女呀</v>
+      </c>
+      <c r="B537" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>佳忱杂货屋</v>
+      </c>
+      <c r="B538" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>小叮当猫</v>
+      </c>
+      <c r="B539" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>科研猎人</v>
+      </c>
+      <c r="B540" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>百宝箱杂货铺</v>
+      </c>
+      <c r="B541" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>是小鱼儿</v>
+      </c>
+      <c r="B542" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>虫乃的周边小铺</v>
+      </c>
+      <c r="B543" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>优选好品质家电馆</v>
+      </c>
+      <c r="B544" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>小馋猫家卡券</v>
+      </c>
+      <c r="B545" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>拾光家选</v>
+      </c>
+      <c r="B546" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>零下一度</v>
+      </c>
+      <c r="B547" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>鱼鱼的小铺</v>
+      </c>
+      <c r="B548" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>花生老板不卖花生</v>
+      </c>
+      <c r="B549" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>正品小家电</v>
+      </c>
+      <c r="B550" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>小黎的拆盒铺</v>
+      </c>
+      <c r="B551" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>时尚包包好看嘛</v>
+      </c>
+      <c r="B552" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>蓝蓝轻奢首饰代购</v>
+      </c>
+      <c r="B553" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>丰川家的店</v>
+      </c>
+      <c r="B554" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>阿滢的小店</v>
+      </c>
+      <c r="B555" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>悠悠妈妈清闲置</v>
+      </c>
+      <c r="B556" t="str">
+        <v>2026-03-22</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B513"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B556"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/input/点赞_用户列表.xlsx
+++ b/input/点赞_用户列表.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B552"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -572,7 +572,7 @@
         <v>麤麤酱二次元</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-01-20</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="23">
@@ -1636,7 +1636,7 @@
         <v>CC妙脆角</v>
       </c>
       <c r="B155" t="str">
-        <v>2026-01-14</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="156">
@@ -2068,7 +2068,7 @@
         <v>莫言會拍照</v>
       </c>
       <c r="B209" t="str">
-        <v>2026-01-13</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="210">
@@ -2116,7 +2116,7 @@
         <v>小艾解忧铺</v>
       </c>
       <c r="B215" t="str">
-        <v>2026-01-18</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="216">
@@ -2820,7 +2820,7 @@
         <v>挪威唱民歌的芝士</v>
       </c>
       <c r="B303" t="str">
-        <v>2026-02-06</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="304">
@@ -3020,7 +3020,7 @@
         <v>娜娜是我呀</v>
       </c>
       <c r="B328" t="str">
-        <v>2026-01-18</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="329">
@@ -3212,7 +3212,7 @@
         <v>小桔子家电批发</v>
       </c>
       <c r="B352" t="str">
-        <v>2026-01-20</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="353">
@@ -3436,7 +3436,7 @@
         <v>淡淡的咸鱼</v>
       </c>
       <c r="B380" t="str">
-        <v>2026-01-17</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="381">
@@ -3812,7 +3812,7 @@
         <v>娜娜的口袋</v>
       </c>
       <c r="B427" t="str">
-        <v>2026-01-18</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="428">
@@ -4236,7 +4236,7 @@
         <v>暖家优选小家电</v>
       </c>
       <c r="B480" t="str">
-        <v>2026-02-06</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="481">
@@ -4324,7 +4324,7 @@
         <v>强者资源库</v>
       </c>
       <c r="B491" t="str">
-        <v>2026-02-06</v>
+        <v>2026-03-23</v>
       </c>
     </row>
     <row r="492">
@@ -4503,9 +4503,321 @@
         <v>2026-02-06</v>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>柠源优品</v>
+      </c>
+      <c r="B514" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>甜净生活馆</v>
+      </c>
+      <c r="B515" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>壹人小家电</v>
+      </c>
+      <c r="B516" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>橘子味的秋天</v>
+      </c>
+      <c r="B517" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>品质家电严选店</v>
+      </c>
+      <c r="B518" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>小杨数码科技</v>
+      </c>
+      <c r="B519" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>智享科技</v>
+      </c>
+      <c r="B520" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>伊伊家电</v>
+      </c>
+      <c r="B521" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>羽球小哥的二手球</v>
+      </c>
+      <c r="B522" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>小云严选数码</v>
+      </c>
+      <c r="B523" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>狸狸次元屋</v>
+      </c>
+      <c r="B524" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>毛毛的玩偶屋</v>
+      </c>
+      <c r="B525" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>G小王子</v>
+      </c>
+      <c r="B526" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>小枝百货铺</v>
+      </c>
+      <c r="B527" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>大鱼和小余店铺</v>
+      </c>
+      <c r="B528" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
+        <v>布偶猫的百宝袋</v>
+      </c>
+      <c r="B529" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
+        <v>乐乐严选家电</v>
+      </c>
+      <c r="B530" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>小E的宝藏清单</v>
+      </c>
+      <c r="B531" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>美术馆会玩的翻车鱼</v>
+      </c>
+      <c r="B532" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>诚品数码铺</v>
+      </c>
+      <c r="B533" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v/>
+      </c>
+      <c r="B534" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>海伦的小店铺</v>
+      </c>
+      <c r="B535" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>快乐小宝</v>
+      </c>
+      <c r="B536" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>六一小仙女呀</v>
+      </c>
+      <c r="B537" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>佳忱杂货屋</v>
+      </c>
+      <c r="B538" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>小叮当猫</v>
+      </c>
+      <c r="B539" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>科研猎人</v>
+      </c>
+      <c r="B540" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>百宝箱杂货铺</v>
+      </c>
+      <c r="B541" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>是小鱼儿</v>
+      </c>
+      <c r="B542" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>虫乃的周边小铺</v>
+      </c>
+      <c r="B543" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>优选好品质家电馆</v>
+      </c>
+      <c r="B544" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>小馋猫家卡券</v>
+      </c>
+      <c r="B545" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>拾光家选</v>
+      </c>
+      <c r="B546" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>零下一度</v>
+      </c>
+      <c r="B547" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>鱼鱼的小铺</v>
+      </c>
+      <c r="B548" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>花生老板不卖花生</v>
+      </c>
+      <c r="B549" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>正品小家电</v>
+      </c>
+      <c r="B550" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>小黎的拆盒铺</v>
+      </c>
+      <c r="B551" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>时尚包包好看嘛</v>
+      </c>
+      <c r="B552" t="str">
+        <v>2026-03-23</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B513"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B552"/>
   </ignoredErrors>
 </worksheet>
 </file>